--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/76.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/76.xlsx
@@ -426,13 +426,13 @@
         <v>-10.27972548228822</v>
       </c>
       <c r="E2">
-        <v>-12.28382745806402</v>
+        <v>-11.55599300165521</v>
       </c>
       <c r="F2">
-        <v>-3.398884378082993</v>
+        <v>-3.445571993272176</v>
       </c>
       <c r="G2">
-        <v>-12.219959677228</v>
+        <v>-10.04231923749635</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.839510301049945</v>
       </c>
       <c r="E3">
-        <v>-12.62267505416196</v>
+        <v>-12.22349912733384</v>
       </c>
       <c r="F3">
-        <v>-3.455123069426454</v>
+        <v>-3.29948857342108</v>
       </c>
       <c r="G3">
-        <v>-11.49221569351218</v>
+        <v>-9.090663195686375</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.459300455960671</v>
       </c>
       <c r="E4">
-        <v>-13.08170835042348</v>
+        <v>-13.35117972472391</v>
       </c>
       <c r="F4">
-        <v>-3.338160077253372</v>
+        <v>-3.332701964436326</v>
       </c>
       <c r="G4">
-        <v>-12.25063850274043</v>
+        <v>-9.937182932260175</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.207694551654161</v>
       </c>
       <c r="E5">
-        <v>-13.59123413187051</v>
+        <v>-13.51896874365611</v>
       </c>
       <c r="F5">
-        <v>-3.227746157766823</v>
+        <v>-3.566304057127995</v>
       </c>
       <c r="G5">
-        <v>-11.67773535498739</v>
+        <v>-9.523834837317853</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.069345213288628</v>
       </c>
       <c r="E6">
-        <v>-14.26465444460316</v>
+        <v>-15.28081231260633</v>
       </c>
       <c r="F6">
-        <v>-3.515720630043446</v>
+        <v>-3.584828008989398</v>
       </c>
       <c r="G6">
-        <v>-11.18204075030124</v>
+        <v>-9.238889561661702</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.027952693164378</v>
       </c>
       <c r="E7">
-        <v>-15.31254785845209</v>
+        <v>-15.82364502037979</v>
       </c>
       <c r="F7">
-        <v>-3.356026305396952</v>
+        <v>-3.596640528153319</v>
       </c>
       <c r="G7">
-        <v>-11.14868369344754</v>
+        <v>-9.080933502346456</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.055855112170546</v>
       </c>
       <c r="E8">
-        <v>-16.46293875299063</v>
+        <v>-16.47158360987127</v>
       </c>
       <c r="F8">
-        <v>-3.359158362546937</v>
+        <v>-3.428182904752608</v>
       </c>
       <c r="G8">
-        <v>-10.27036947751458</v>
+        <v>-9.00265565307039</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.122237560135218</v>
       </c>
       <c r="E9">
-        <v>-17.18014488090343</v>
+        <v>-17.27890184206271</v>
       </c>
       <c r="F9">
-        <v>-3.348800456542332</v>
+        <v>-3.387314570568092</v>
       </c>
       <c r="G9">
-        <v>-11.02619350849451</v>
+        <v>-8.006019229018339</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.179330956900284</v>
       </c>
       <c r="E10">
-        <v>-18.28262904891483</v>
+        <v>-18.77553985922772</v>
       </c>
       <c r="F10">
-        <v>-3.156865244211478</v>
+        <v>-3.318664450428486</v>
       </c>
       <c r="G10">
-        <v>-11.02643848886442</v>
+        <v>-8.475855162497243</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.193600800514684</v>
       </c>
       <c r="E11">
-        <v>-18.70077022488708</v>
+        <v>-19.61169994237402</v>
       </c>
       <c r="F11">
-        <v>-3.33267048647502</v>
+        <v>-3.440675513554228</v>
       </c>
       <c r="G11">
-        <v>-10.01017384031003</v>
+        <v>-7.996898676057646</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.130236956562557</v>
       </c>
       <c r="E12">
-        <v>-20.03919241717211</v>
+        <v>-20.1495875565311</v>
       </c>
       <c r="F12">
-        <v>-3.149822464552877</v>
+        <v>-3.529659568330354</v>
       </c>
       <c r="G12">
-        <v>-9.749349199453006</v>
+        <v>-6.891881612140934</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.962468716235122</v>
       </c>
       <c r="E13">
-        <v>-20.79197423688917</v>
+        <v>-20.92288789197692</v>
       </c>
       <c r="F13">
-        <v>-3.036667477330464</v>
+        <v>-3.244032689273264</v>
       </c>
       <c r="G13">
-        <v>-8.79665695688924</v>
+        <v>-6.923103367121801</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.693727316871716</v>
       </c>
       <c r="E14">
-        <v>-21.43541605169104</v>
+        <v>-22.04730798808147</v>
       </c>
       <c r="F14">
-        <v>-2.96229830864193</v>
+        <v>-3.000280610795093</v>
       </c>
       <c r="G14">
-        <v>-9.218506532776409</v>
+        <v>-6.20018615880223</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.341397157938303</v>
       </c>
       <c r="E15">
-        <v>-21.92459992789562</v>
+        <v>-23.28620790709992</v>
       </c>
       <c r="F15">
-        <v>-2.906782782041113</v>
+        <v>-3.087475391981172</v>
       </c>
       <c r="G15">
-        <v>-8.487620841343814</v>
+        <v>-5.106259422442077</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.940942950869694</v>
       </c>
       <c r="E16">
-        <v>-22.65641038448317</v>
+        <v>-23.18241528284412</v>
       </c>
       <c r="F16">
-        <v>-3.012682099182404</v>
+        <v>-3.01073957762284</v>
       </c>
       <c r="G16">
-        <v>-8.550044488032311</v>
+        <v>-5.209584859268269</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.543092929509828</v>
       </c>
       <c r="E17">
-        <v>-24.66469803740482</v>
+        <v>-24.25160158147711</v>
       </c>
       <c r="F17">
-        <v>-2.493082847204595</v>
+        <v>-2.972251142986566</v>
       </c>
       <c r="G17">
-        <v>-7.524424237783941</v>
+        <v>-5.048381154778999</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.185181122532479</v>
       </c>
       <c r="E18">
-        <v>-24.55202960409398</v>
+        <v>-25.57858031994476</v>
       </c>
       <c r="F18">
-        <v>-2.245314843557652</v>
+        <v>-2.745949452215769</v>
       </c>
       <c r="G18">
-        <v>-7.495364269040218</v>
+        <v>-4.608174603876569</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.889393924929044</v>
       </c>
       <c r="E19">
-        <v>-26.13381198955121</v>
+        <v>-26.46306827770091</v>
       </c>
       <c r="F19">
-        <v>-2.126483054523854</v>
+        <v>-2.281193920875107</v>
       </c>
       <c r="G19">
-        <v>-7.082168459192703</v>
+        <v>-4.246580267349675</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.659658412316984</v>
       </c>
       <c r="E20">
-        <v>-26.3622870886602</v>
+        <v>-26.8021785252913</v>
       </c>
       <c r="F20">
-        <v>-2.190077648404175</v>
+        <v>-2.202623272719574</v>
       </c>
       <c r="G20">
-        <v>-7.22063202637272</v>
+        <v>-4.045454694202332</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.473865707066217</v>
       </c>
       <c r="E21">
-        <v>-27.31519576019825</v>
+        <v>-27.34706263179022</v>
       </c>
       <c r="F21">
-        <v>-2.04651826402941</v>
+        <v>-1.890638571272807</v>
       </c>
       <c r="G21">
-        <v>-7.037714453691369</v>
+        <v>-3.919779764440519</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.305278168150821</v>
       </c>
       <c r="E22">
-        <v>-27.5435848183011</v>
+        <v>-28.57296583040667</v>
       </c>
       <c r="F22">
-        <v>-1.357202270198635</v>
+        <v>-1.768928205514281</v>
       </c>
       <c r="G22">
-        <v>-7.324718888672946</v>
+        <v>-3.495811439408215</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.126684339362469</v>
       </c>
       <c r="E23">
-        <v>-28.31557189628469</v>
+        <v>-28.96844652244453</v>
       </c>
       <c r="F23">
-        <v>-1.553839295907778</v>
+        <v>-1.602655815322156</v>
       </c>
       <c r="G23">
-        <v>-7.168706119589252</v>
+        <v>-3.8468252723916</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.909932571027825</v>
       </c>
       <c r="E24">
-        <v>-28.45575986614014</v>
+        <v>-29.56068488164167</v>
       </c>
       <c r="F24">
-        <v>-1.323410678736234</v>
+        <v>-1.323093414020962</v>
       </c>
       <c r="G24">
-        <v>-7.073435240060105</v>
+        <v>-3.604725077104698</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.643958675471398</v>
       </c>
       <c r="E25">
-        <v>-29.20621405021727</v>
+        <v>-30.2647991911983</v>
       </c>
       <c r="F25">
-        <v>-1.291106835129262</v>
+        <v>-1.201900777889186</v>
       </c>
       <c r="G25">
-        <v>-7.624435818525323</v>
+        <v>-3.491123706924607</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.327060750597743</v>
       </c>
       <c r="E26">
-        <v>-28.829983901186</v>
+        <v>-29.8829944906636</v>
       </c>
       <c r="F26">
-        <v>-1.396060985063959</v>
+        <v>-1.489731114237722</v>
       </c>
       <c r="G26">
-        <v>-7.329863476440972</v>
+        <v>-3.910496994748403</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.96427831949903</v>
       </c>
       <c r="E27">
-        <v>-29.14217237080079</v>
+        <v>-29.514831818077</v>
       </c>
       <c r="F27">
-        <v>-1.308147180972251</v>
+        <v>-1.405104272000322</v>
       </c>
       <c r="G27">
-        <v>-7.460358560507965</v>
+        <v>-4.580879155905278</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.580750915502497</v>
       </c>
       <c r="E28">
-        <v>-28.8217737778101</v>
+        <v>-29.51633527144755</v>
       </c>
       <c r="F28">
-        <v>-1.217402017097773</v>
+        <v>-1.278087384659462</v>
       </c>
       <c r="G28">
-        <v>-7.228514435301725</v>
+        <v>-4.885843300437402</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.20382554034951</v>
       </c>
       <c r="E29">
-        <v>-29.02726687133016</v>
+        <v>-29.29830056916324</v>
       </c>
       <c r="F29">
-        <v>-1.055746946808853</v>
+        <v>-1.247684644241915</v>
       </c>
       <c r="G29">
-        <v>-7.73292239584724</v>
+        <v>-4.723987418476893</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.863050267405657</v>
       </c>
       <c r="E30">
-        <v>-28.56586518316264</v>
+        <v>-29.61636926227699</v>
       </c>
       <c r="F30">
-        <v>-1.356764063842554</v>
+        <v>-1.564963441759973</v>
       </c>
       <c r="G30">
-        <v>-7.604857252206073</v>
+        <v>-4.718892488891955</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.591824576841255</v>
       </c>
       <c r="E31">
-        <v>-29.16771296420405</v>
+        <v>-29.29871266029794</v>
       </c>
       <c r="F31">
-        <v>-1.4137971595253</v>
+        <v>-1.279649685581142</v>
       </c>
       <c r="G31">
-        <v>-7.948008539533689</v>
+        <v>-5.332177671133021</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.410925708965642</v>
       </c>
       <c r="E32">
-        <v>-27.96701978038831</v>
+        <v>-29.13963189688249</v>
       </c>
       <c r="F32">
-        <v>-1.449731737458742</v>
+        <v>-1.376287026791732</v>
       </c>
       <c r="G32">
-        <v>-7.437135083549977</v>
+        <v>-4.451241503132958</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.336272219471753</v>
       </c>
       <c r="E33">
-        <v>-28.26747950232323</v>
+        <v>-28.9700224313992</v>
       </c>
       <c r="F33">
-        <v>-1.270070444935169</v>
+        <v>-1.520234087111008</v>
       </c>
       <c r="G33">
-        <v>-7.719183631859265</v>
+        <v>-4.552203210444111</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.376044160972866</v>
       </c>
       <c r="E34">
-        <v>-26.8647031659152</v>
+        <v>-29.31891871132017</v>
       </c>
       <c r="F34">
-        <v>-1.126260065237355</v>
+        <v>-1.495587671775514</v>
       </c>
       <c r="G34">
-        <v>-7.160813779023629</v>
+        <v>-4.116585075659112</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.520982501353424</v>
       </c>
       <c r="E35">
-        <v>-27.74649668163679</v>
+        <v>-27.82398792885604</v>
       </c>
       <c r="F35">
-        <v>-0.9058439248634483</v>
+        <v>-1.382947929077643</v>
       </c>
       <c r="G35">
-        <v>-7.93483256828739</v>
+        <v>-3.990440048430723</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.759854622909933</v>
       </c>
       <c r="E36">
-        <v>-26.63054030345257</v>
+        <v>-28.19695757660178</v>
       </c>
       <c r="F36">
-        <v>-1.323722144879687</v>
+        <v>-1.596697368593819</v>
       </c>
       <c r="G36">
-        <v>-7.198312328346954</v>
+        <v>-4.255608125035267</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.072786443805104</v>
       </c>
       <c r="E37">
-        <v>-26.89068754977121</v>
+        <v>-27.04153554744072</v>
       </c>
       <c r="F37">
-        <v>-1.368757167100285</v>
+        <v>-1.611833297777772</v>
       </c>
       <c r="G37">
-        <v>-6.337901542690372</v>
+        <v>-4.445034230246825</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.431943721675009</v>
       </c>
       <c r="E38">
-        <v>-27.16566101999096</v>
+        <v>-27.10094006947334</v>
       </c>
       <c r="F38">
-        <v>-1.572089058158854</v>
+        <v>-1.764899026467065</v>
       </c>
       <c r="G38">
-        <v>-6.299462798433894</v>
+        <v>-4.220920228874784</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.818131672733318</v>
       </c>
       <c r="E39">
-        <v>-26.71082109066055</v>
+        <v>-26.20514451212004</v>
       </c>
       <c r="F39">
-        <v>-1.653115815663688</v>
+        <v>-1.914848436987025</v>
       </c>
       <c r="G39">
-        <v>-6.537255973974204</v>
+        <v>-3.605599061127065</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.208871481445307</v>
       </c>
       <c r="E40">
-        <v>-25.36129055163471</v>
+        <v>-26.96995848727548</v>
       </c>
       <c r="F40">
-        <v>-1.51392027076687</v>
+        <v>-1.86145518767218</v>
       </c>
       <c r="G40">
-        <v>-6.16044305960328</v>
+        <v>-3.685922827546402</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.58429903094053</v>
       </c>
       <c r="E41">
-        <v>-24.92155308311988</v>
+        <v>-25.90504253963172</v>
       </c>
       <c r="F41">
-        <v>-1.615802006004584</v>
+        <v>-1.783055183201624</v>
       </c>
       <c r="G41">
-        <v>-6.432990342214858</v>
+        <v>-3.106338998895117</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.93786903054937</v>
       </c>
       <c r="E42">
-        <v>-24.72126773470864</v>
+        <v>-24.60230925100114</v>
       </c>
       <c r="F42">
-        <v>-1.765520302019164</v>
+        <v>-2.052276245846269</v>
       </c>
       <c r="G42">
-        <v>-5.409233929105097</v>
+        <v>-3.764002044090113</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.261859559206388</v>
       </c>
       <c r="E43">
-        <v>-24.599270644942</v>
+        <v>-25.52501300090803</v>
       </c>
       <c r="F43">
-        <v>-1.543812736864293</v>
+        <v>-2.107023047497288</v>
       </c>
       <c r="G43">
-        <v>-5.933690553436438</v>
+        <v>-2.678305323940588</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.555017053065461</v>
       </c>
       <c r="E44">
-        <v>-24.25338127176213</v>
+        <v>-24.45009365418132</v>
       </c>
       <c r="F44">
-        <v>-1.869386805553986</v>
+        <v>-1.889392706698997</v>
       </c>
       <c r="G44">
-        <v>-6.108497289546575</v>
+        <v>-3.355440997997578</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.823245207457888</v>
       </c>
       <c r="E45">
-        <v>-23.84822775924388</v>
+        <v>-24.26294088039232</v>
       </c>
       <c r="F45">
-        <v>-1.691125453941143</v>
+        <v>-2.161884163849894</v>
       </c>
       <c r="G45">
-        <v>-5.816483999164082</v>
+        <v>-3.314562381678657</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.06913701636325</v>
       </c>
       <c r="E46">
-        <v>-23.11743620930806</v>
+        <v>-23.32477692022325</v>
       </c>
       <c r="F46">
-        <v>-1.754015935529085</v>
+        <v>-1.928518155868023</v>
       </c>
       <c r="G46">
-        <v>-5.47458409805031</v>
+        <v>-3.40089809879731</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.303151282134323</v>
       </c>
       <c r="E47">
-        <v>-22.3680235742527</v>
+        <v>-23.32016240520943</v>
       </c>
       <c r="F47">
-        <v>-1.836380506389439</v>
+        <v>-2.199781972527971</v>
       </c>
       <c r="G47">
-        <v>-6.245431384687449</v>
+        <v>-3.274660376293821</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.535730425856793</v>
       </c>
       <c r="E48">
-        <v>-22.48338192112409</v>
+        <v>-22.37184560631517</v>
       </c>
       <c r="F48">
-        <v>-2.079477346251996</v>
+        <v>-2.190325330257612</v>
       </c>
       <c r="G48">
-        <v>-5.865294682595096</v>
+        <v>-3.362028983620727</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.767608809574305</v>
       </c>
       <c r="E49">
-        <v>-22.8573976463656</v>
+        <v>-21.47068833573679</v>
       </c>
       <c r="F49">
-        <v>-2.110712595909357</v>
+        <v>-2.341513978412161</v>
       </c>
       <c r="G49">
-        <v>-6.147664353821693</v>
+        <v>-3.4430049275113</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.00601281925934</v>
       </c>
       <c r="E50">
-        <v>-21.78301718804581</v>
+        <v>-21.81383345366801</v>
       </c>
       <c r="F50">
-        <v>-2.146273580144137</v>
+        <v>-2.200472002574503</v>
       </c>
       <c r="G50">
-        <v>-5.784626619439675</v>
+        <v>-3.064543361461818</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.252201332290053</v>
       </c>
       <c r="E51">
-        <v>-21.71986308953484</v>
+        <v>-20.8093499916566</v>
       </c>
       <c r="F51">
-        <v>-2.33849540759636</v>
+        <v>-2.535650162932253</v>
       </c>
       <c r="G51">
-        <v>-6.930621616041486</v>
+        <v>-3.427792970758349</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.499357800952398</v>
       </c>
       <c r="E52">
-        <v>-20.40942686661721</v>
+        <v>-21.03654353262143</v>
       </c>
       <c r="F52">
-        <v>-2.109972863818657</v>
+        <v>-2.380162287957175</v>
       </c>
       <c r="G52">
-        <v>-6.375943021482137</v>
+        <v>-3.660186646524108</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.751371545291503</v>
       </c>
       <c r="E53">
-        <v>-20.01577114960444</v>
+        <v>-20.65780008051591</v>
       </c>
       <c r="F53">
-        <v>-2.396181256792512</v>
+        <v>-2.295746679407488</v>
       </c>
       <c r="G53">
-        <v>-5.779372783668852</v>
+        <v>-3.689587601458375</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.0057020361896</v>
       </c>
       <c r="E54">
-        <v>-19.4247147221233</v>
+        <v>-20.04228989339335</v>
       </c>
       <c r="F54">
-        <v>-2.47796679883831</v>
+        <v>-2.337982648174027</v>
       </c>
       <c r="G54">
-        <v>-6.167838818338011</v>
+        <v>-4.129353849804081</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.256741933099562</v>
       </c>
       <c r="E55">
-        <v>-19.67489026867705</v>
+        <v>-19.29509621060175</v>
       </c>
       <c r="F55">
-        <v>-2.650751813551245</v>
+        <v>-2.348314874789145</v>
       </c>
       <c r="G55">
-        <v>-6.731604860402658</v>
+        <v>-3.670820118796247</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.509617236668706</v>
       </c>
       <c r="E56">
-        <v>-17.98723216092048</v>
+        <v>-18.56564961744621</v>
       </c>
       <c r="F56">
-        <v>-2.308105092689854</v>
+        <v>-2.44235859766157</v>
       </c>
       <c r="G56">
-        <v>-6.887276643295808</v>
+        <v>-4.619086161974008</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.760170161738541</v>
       </c>
       <c r="E57">
-        <v>-18.4423075708993</v>
+        <v>-17.17258685778463</v>
       </c>
       <c r="F57">
-        <v>-2.463253337029785</v>
+        <v>-2.458302185063252</v>
       </c>
       <c r="G57">
-        <v>-6.782524361342189</v>
+        <v>-4.48339352141036</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.0049883126354</v>
       </c>
       <c r="E58">
-        <v>-18.09510946873121</v>
+        <v>-17.78696492640527</v>
       </c>
       <c r="F58">
-        <v>-2.453397421671276</v>
+        <v>-2.503056390734301</v>
       </c>
       <c r="G58">
-        <v>-7.661182874011233</v>
+        <v>-4.838131718125425</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.24857667559104</v>
       </c>
       <c r="E59">
-        <v>-18.10472341904949</v>
+        <v>-17.98407581453714</v>
       </c>
       <c r="F59">
-        <v>-2.349128331578694</v>
+        <v>-2.470252213216038</v>
       </c>
       <c r="G59">
-        <v>-7.159095605888747</v>
+        <v>-4.861053935439339</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.48463215270792</v>
       </c>
       <c r="E60">
-        <v>-16.95238075221365</v>
+        <v>-17.04663188173529</v>
       </c>
       <c r="F60">
-        <v>-2.400614679132294</v>
+        <v>-2.617571557232111</v>
       </c>
       <c r="G60">
-        <v>-7.236175037679598</v>
+        <v>-5.155771941527417</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.71224771680029</v>
       </c>
       <c r="E61">
-        <v>-17.72017899174015</v>
+        <v>-16.88085350526249</v>
       </c>
       <c r="F61">
-        <v>-2.694382753024097</v>
+        <v>-2.808427406837116</v>
       </c>
       <c r="G61">
-        <v>-7.494241994102405</v>
+        <v>-5.425581402978018</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.93272881294665</v>
       </c>
       <c r="E62">
-        <v>-16.69011870853343</v>
+        <v>-16.74256749449026</v>
       </c>
       <c r="F62">
-        <v>-2.76962750605739</v>
+        <v>-2.826609242961163</v>
       </c>
       <c r="G62">
-        <v>-8.066483032747588</v>
+        <v>-5.653459494628211</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.13642143907198</v>
       </c>
       <c r="E63">
-        <v>-15.94191517603811</v>
+        <v>-16.64979264749512</v>
       </c>
       <c r="F63">
-        <v>-2.681491699501731</v>
+        <v>-2.641455874557029</v>
       </c>
       <c r="G63">
-        <v>-8.381812495363167</v>
+        <v>-5.177677821360774</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.32511831687877</v>
       </c>
       <c r="E64">
-        <v>-15.66572807478431</v>
+        <v>-16.33355572211748</v>
       </c>
       <c r="F64">
-        <v>-2.552306974667746</v>
+        <v>-2.581928564624453</v>
       </c>
       <c r="G64">
-        <v>-8.435344016733183</v>
+        <v>-5.974622138483988</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.49864341073032</v>
       </c>
       <c r="E65">
-        <v>-15.34464568221845</v>
+        <v>-15.60299965283006</v>
       </c>
       <c r="F65">
-        <v>-2.812419309351207</v>
+        <v>-2.702201712939122</v>
       </c>
       <c r="G65">
-        <v>-8.498436393620613</v>
+        <v>-5.953414783759417</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.64755620397418</v>
       </c>
       <c r="E66">
-        <v>-15.6627709812573</v>
+        <v>-14.94688263928072</v>
       </c>
       <c r="F66">
-        <v>-2.724945368350385</v>
+        <v>-2.822976023532484</v>
       </c>
       <c r="G66">
-        <v>-8.922576867020959</v>
+        <v>-6.298747720597412</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.77654161026403</v>
       </c>
       <c r="E67">
-        <v>-15.5170039314244</v>
+        <v>-15.87459488144009</v>
       </c>
       <c r="F67">
-        <v>-2.693109552325994</v>
+        <v>-2.87691682370058</v>
       </c>
       <c r="G67">
-        <v>-9.019380529134787</v>
+        <v>-6.544966234535167</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.8833892704972</v>
       </c>
       <c r="E68">
-        <v>-14.57047135128915</v>
+        <v>-15.63012974061001</v>
       </c>
       <c r="F68">
-        <v>-2.705427375605623</v>
+        <v>-3.04569419691877</v>
       </c>
       <c r="G68">
-        <v>-10.46777730802132</v>
+        <v>-6.186162687897878</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.96001068348776</v>
       </c>
       <c r="E69">
-        <v>-14.51195893863605</v>
+        <v>-14.49330162572444</v>
       </c>
       <c r="F69">
-        <v>-2.550504447199254</v>
+        <v>-2.80502861538343</v>
       </c>
       <c r="G69">
-        <v>-9.197679890788855</v>
+        <v>-6.755331540282615</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.01246535449451</v>
       </c>
       <c r="E70">
-        <v>-15.14469544088378</v>
+        <v>-15.13757215126971</v>
       </c>
       <c r="F70">
-        <v>-2.89927197479993</v>
+        <v>-2.975109010526225</v>
       </c>
       <c r="G70">
-        <v>-9.520656713600152</v>
+        <v>-6.890974522663174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.03777086336155</v>
       </c>
       <c r="E71">
-        <v>-14.56127854905358</v>
+        <v>-14.90800568992487</v>
       </c>
       <c r="F71">
-        <v>-2.815902594279979</v>
+        <v>-3.24932181514014</v>
       </c>
       <c r="G71">
-        <v>-10.18176603670153</v>
+        <v>-6.793306808163595</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.03041322961123</v>
       </c>
       <c r="E72">
-        <v>-15.80243364812786</v>
+        <v>-15.06629397038898</v>
       </c>
       <c r="F72">
-        <v>-2.820692214602966</v>
+        <v>-2.935842738898722</v>
       </c>
       <c r="G72">
-        <v>-9.3827129020698</v>
+        <v>-6.448073187691778</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.99668803552739</v>
       </c>
       <c r="E73">
-        <v>-14.69201106518102</v>
+        <v>-13.98119914256704</v>
       </c>
       <c r="F73">
-        <v>-2.804653364949962</v>
+        <v>-3.294293881438124</v>
       </c>
       <c r="G73">
-        <v>-10.06357625040401</v>
+        <v>-7.065632284224043</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.93297063193444</v>
       </c>
       <c r="E74">
-        <v>-15.54408420599026</v>
+        <v>-15.17216969268831</v>
       </c>
       <c r="F74">
-        <v>-2.793590518285574</v>
+        <v>-3.381772792643364</v>
       </c>
       <c r="G74">
-        <v>-10.13933808507023</v>
+        <v>-7.212656922168616</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.84141757468957</v>
       </c>
       <c r="E75">
-        <v>-16.10266241788839</v>
+        <v>-15.20022358916583</v>
       </c>
       <c r="F75">
-        <v>-2.894260352012993</v>
+        <v>-3.348510527951352</v>
       </c>
       <c r="G75">
-        <v>-9.891262355084944</v>
+        <v>-6.775409998978295</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.73252636403502</v>
       </c>
       <c r="E76">
-        <v>-16.01963737543176</v>
+        <v>-15.49047613068746</v>
       </c>
       <c r="F76">
-        <v>-3.270764933729007</v>
+        <v>-3.557848911047621</v>
       </c>
       <c r="G76">
-        <v>-9.209283352904</v>
+        <v>-7.073147222598188</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.60526579919121</v>
       </c>
       <c r="E77">
-        <v>-16.72526872378096</v>
+        <v>-15.5403255725639</v>
       </c>
       <c r="F77">
-        <v>-2.799657481143678</v>
+        <v>-3.394904072712541</v>
       </c>
       <c r="G77">
-        <v>-8.770755248589982</v>
+        <v>-7.006942932903844</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.46768387486211</v>
       </c>
       <c r="E78">
-        <v>-16.50451920132906</v>
+        <v>-15.72549940321155</v>
       </c>
       <c r="F78">
-        <v>-3.179174006736272</v>
+        <v>-3.419867752763307</v>
       </c>
       <c r="G78">
-        <v>-9.452482649309941</v>
+        <v>-6.717349651310557</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.32887537120876</v>
       </c>
       <c r="E79">
-        <v>-16.66820995128431</v>
+        <v>-16.69300787495032</v>
       </c>
       <c r="F79">
-        <v>-3.121837728584101</v>
+        <v>-3.561852410705351</v>
       </c>
       <c r="G79">
-        <v>-9.939712189052177</v>
+        <v>-6.696095948948436</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.18498337282746</v>
       </c>
       <c r="E80">
-        <v>-17.21428504644726</v>
+        <v>-16.45785327668001</v>
       </c>
       <c r="F80">
-        <v>-3.154114236066781</v>
+        <v>-3.590236419762276</v>
       </c>
       <c r="G80">
-        <v>-9.692632933274211</v>
+        <v>-6.289004785075337</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.04417644899832</v>
       </c>
       <c r="E81">
-        <v>-18.07157046083934</v>
+        <v>-17.62595503306255</v>
       </c>
       <c r="F81">
-        <v>-3.320967311808269</v>
+        <v>-3.548567054299252</v>
       </c>
       <c r="G81">
-        <v>-9.118034786205069</v>
+        <v>-6.309258702684597</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.90836691849753</v>
       </c>
       <c r="E82">
-        <v>-18.70995849864864</v>
+        <v>-18.27331850635506</v>
       </c>
       <c r="F82">
-        <v>-3.574148696432506</v>
+        <v>-3.858504859893702</v>
       </c>
       <c r="G82">
-        <v>-9.096754599478635</v>
+        <v>-6.501045226865656</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.77074420093201</v>
       </c>
       <c r="E83">
-        <v>-19.61302678525827</v>
+        <v>-18.79262579165866</v>
       </c>
       <c r="F83">
-        <v>-3.692756826267548</v>
+        <v>-3.742577326974119</v>
       </c>
       <c r="G83">
-        <v>-9.030775426880959</v>
+        <v>-6.109136224835654</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.63859999635347</v>
       </c>
       <c r="E84">
-        <v>-20.95185201172998</v>
+        <v>-19.24257496906079</v>
       </c>
       <c r="F84">
-        <v>-3.581861625319973</v>
+        <v>-3.95728104573832</v>
       </c>
       <c r="G84">
-        <v>-9.442143815590796</v>
+        <v>-5.842124174365737</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.51155693721864</v>
       </c>
       <c r="E85">
-        <v>-20.42206130909861</v>
+        <v>-19.84193208939799</v>
       </c>
       <c r="F85">
-        <v>-3.667561203343999</v>
+        <v>-3.962894063259689</v>
       </c>
       <c r="G85">
-        <v>-9.159472884720126</v>
+        <v>-6.188847540330226</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.38507235376773</v>
       </c>
       <c r="E86">
-        <v>-21.71315641952948</v>
+        <v>-21.79280774885039</v>
       </c>
       <c r="F86">
-        <v>-3.63668463677205</v>
+        <v>-4.09503026114985</v>
       </c>
       <c r="G86">
-        <v>-8.34223823398672</v>
+        <v>-5.809601374987936</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.26823947222953</v>
       </c>
       <c r="E87">
-        <v>-23.38113377924871</v>
+        <v>-22.89152875496141</v>
       </c>
       <c r="F87">
-        <v>-3.871478750156347</v>
+        <v>-4.147684606741397</v>
       </c>
       <c r="G87">
-        <v>-9.20719770921426</v>
+        <v>-5.786367966393332</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.15842692081418</v>
       </c>
       <c r="E88">
-        <v>-24.92357731100131</v>
+        <v>-23.5251800089587</v>
       </c>
       <c r="F88">
-        <v>-3.782720839681186</v>
+        <v>-4.076372942136596</v>
       </c>
       <c r="G88">
-        <v>-8.644812164639488</v>
+        <v>-5.791956167263622</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.0545211733298</v>
       </c>
       <c r="E89">
-        <v>-26.70769644359526</v>
+        <v>-25.08222334091202</v>
       </c>
       <c r="F89">
-        <v>-4.24023312645177</v>
+        <v>-4.122316683398066</v>
       </c>
       <c r="G89">
-        <v>-8.254515398287111</v>
+        <v>-5.749518283995704</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.962921027761031</v>
       </c>
       <c r="E90">
-        <v>-27.45944124276457</v>
+        <v>-27.02143365132067</v>
       </c>
       <c r="F90">
-        <v>-4.246190744812703</v>
+        <v>-4.242159909030681</v>
       </c>
       <c r="G90">
-        <v>-8.929634950110685</v>
+        <v>-5.917511917386021</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.878390537328816</v>
       </c>
       <c r="E91">
-        <v>-28.64077520019752</v>
+        <v>-29.44407441170716</v>
       </c>
       <c r="F91">
-        <v>-3.972319227568742</v>
+        <v>-4.421572691333415</v>
       </c>
       <c r="G91">
-        <v>-8.99243268844512</v>
+        <v>-6.251456577568923</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.803103707444887</v>
       </c>
       <c r="E92">
-        <v>-31.02172456463239</v>
+        <v>-30.2927217619296</v>
       </c>
       <c r="F92">
-        <v>-4.077087823205212</v>
+        <v>-4.147419529172502</v>
       </c>
       <c r="G92">
-        <v>-8.826001632549339</v>
+        <v>-6.362214189130779</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.740810703792626</v>
       </c>
       <c r="E93">
-        <v>-32.31109432646633</v>
+        <v>-32.20261926008659</v>
       </c>
       <c r="F93">
-        <v>-3.881780327177562</v>
+        <v>-4.52893490530805</v>
       </c>
       <c r="G93">
-        <v>-9.218036435309834</v>
+        <v>-6.411130810019051</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.684281850406416</v>
       </c>
       <c r="E94">
-        <v>-35.31149138617342</v>
+        <v>-34.27157487928901</v>
       </c>
       <c r="F94">
-        <v>-3.953902963469703</v>
+        <v>-4.071481432623066</v>
       </c>
       <c r="G94">
-        <v>-9.534882127782401</v>
+        <v>-6.655266990812605</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.640443023630295</v>
       </c>
       <c r="E95">
-        <v>-37.12997031530058</v>
+        <v>-36.8174331531872</v>
       </c>
       <c r="F95">
-        <v>-3.920812999197475</v>
+        <v>-4.118865704798003</v>
       </c>
       <c r="G95">
-        <v>-9.719650295420204</v>
+        <v>-7.263732018748492</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.61238103860871</v>
       </c>
       <c r="E96">
-        <v>-39.39360050361872</v>
+        <v>-38.34859625618669</v>
       </c>
       <c r="F96">
-        <v>-3.6218452631183</v>
+        <v>-4.075827048018152</v>
       </c>
       <c r="G96">
-        <v>-9.516856207321069</v>
+        <v>-6.903283130978184</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.595732525077633</v>
       </c>
       <c r="E97">
-        <v>-41.70943946877131</v>
+        <v>-40.98340281654354</v>
       </c>
       <c r="F97">
-        <v>-3.876126719653455</v>
+        <v>-3.921215585755235</v>
       </c>
       <c r="G97">
-        <v>-9.641468451964775</v>
+        <v>-7.448622676571248</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.598031793702541</v>
       </c>
       <c r="E98">
-        <v>-43.86435684582432</v>
+        <v>-43.19813227828986</v>
       </c>
       <c r="F98">
-        <v>-3.648573365737028</v>
+        <v>-4.043974664645705</v>
       </c>
       <c r="G98">
-        <v>-9.313608574483053</v>
+        <v>-6.90248197895768</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.615733176975494</v>
       </c>
       <c r="E99">
-        <v>-46.78725812983815</v>
+        <v>-45.44949483052124</v>
       </c>
       <c r="F99">
-        <v>-3.731114378854179</v>
+        <v>-3.820924315930896</v>
       </c>
       <c r="G99">
-        <v>-10.37792248099443</v>
+        <v>-7.709106331237723</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.638603867131726</v>
       </c>
       <c r="E100">
-        <v>-49.18168649715685</v>
+        <v>-48.91552543735602</v>
       </c>
       <c r="F100">
-        <v>-3.407308874569464</v>
+        <v>-3.913691524635607</v>
       </c>
       <c r="G100">
-        <v>-10.4620765486027</v>
+        <v>-7.482406793799511</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.665437927098251</v>
       </c>
       <c r="E101">
-        <v>-51.44008969435164</v>
+        <v>-50.75676221260872</v>
       </c>
       <c r="F101">
-        <v>-3.395934561761624</v>
+        <v>-3.625490079690617</v>
       </c>
       <c r="G101">
-        <v>-10.45827604232362</v>
+        <v>-8.051383634542971</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.684345969445221</v>
       </c>
       <c r="E102">
-        <v>-53.42602253533443</v>
+        <v>-52.70352941401767</v>
       </c>
       <c r="F102">
-        <v>-3.460857028588632</v>
+        <v>-3.689274369706179</v>
       </c>
       <c r="G102">
-        <v>-10.7214577916046</v>
+        <v>-8.165474965462874</v>
       </c>
     </row>
   </sheetData>
